--- a/courses/2/math-modeling/dist/Учебный_план_Математическое_моделирование.xlsx
+++ b/courses/2/math-modeling/dist/Учебный_план_Математическое_моделирование.xlsx
@@ -195,12 +195,12 @@
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Математическое моделирование: цели»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Зачем задачу заменяют моделью: что модель упрощает, какие допущения принимает и как по ней получают числовой ответ, который можно проверить.</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Математическое моделирование: цели</t>
+          <t xml:space="preserve">модель, допущение, адекватность, цель расчёта, оригинал</t>
         </is>
       </c>
     </row>
@@ -225,12 +225,12 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Постановка задачи»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Формулировка задачи для расчёта: что дано, что найти, какие ограничения учесть. Результат: постановка с переменными и критерием на листе Excel.</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Постановка задачи</t>
+          <t xml:space="preserve">переменная, исходные данные, ограничение, критерий, формулировка</t>
         </is>
       </c>
     </row>
@@ -255,12 +255,12 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Постановка задачи»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Переход от текста задачи к формальной постановке: какие величины известны, какие ищут, что ограничивает решение и как выглядит целевая функция.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Постановка задачи</t>
+          <t xml:space="preserve">целевая функция, параметр, ограничение, область допустимых значений, формализация</t>
         </is>
       </c>
     </row>
@@ -285,16 +285,16 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Линейная алгебра в моделях»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Векторы и матрицы как способ записать много связей сразу: система линейных уравнений описывает баланс, а её решение даёт значения всех переменных.</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Линейная алгебра в моделях</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
+          <t xml:space="preserve">матрица, вектор, система уравнений, определитель, метод Гаусса</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="45" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">5-6</t>
@@ -315,12 +315,12 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Расчёты в Excel; Графики в Excel.</t>
+          <t xml:space="preserve">Расчётная таблица в Excel: формулы, абсолютные ссылки, подбор параметра. Итог: книга с расчётом и двумя графиками по полученным значениям.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Расчёты в Excel, Графики в Excel</t>
+          <t xml:space="preserve">формула, абсолютная ссылка, подбор параметра, диаграмма, оси координат</t>
         </is>
       </c>
     </row>
@@ -345,12 +345,12 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Функции и графики»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Функция связывает вход и выход модели, а её график показывает поведение связи: рост, насыщение, разрыв. Коэффициенты сдвигают и растягивают кривую.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Функции и графики</t>
+          <t xml:space="preserve">функция, аргумент, область определения, коэффициент, асимптота</t>
         </is>
       </c>
     </row>
@@ -375,16 +375,16 @@
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Оптимизация в Excel»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Поиск наилучшего варианта в Excel через надстройку «Поиск решения»: задать целевую ячейку, переменные и ограничения, получить ответ и отчёт.</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Оптимизация в Excel</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="45" customHeight="1">
+          <t xml:space="preserve">целевая ячейка, переменные, ограничение, Поиск решения, отчёт</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="60" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">9</t>
@@ -405,12 +405,12 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Производная и оптимизация»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Производная показывает скорость изменения величины, поэтому в точке максимума или минимума она обращается в нуль. Это даёт способ искать оптимум без перебора.</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Производная и оптимизация</t>
+          <t xml:space="preserve">приращение, скорость изменения, экстремум, касательная, критическая точка</t>
         </is>
       </c>
     </row>
@@ -435,16 +435,16 @@
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Интеграл и накопление»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Интеграл складывает малые вклады в общий итог: пройденный путь, израсходованный ресурс, накопленную сумму. Считают его по площади под графиком.</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Интеграл и накопление</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
+          <t xml:space="preserve">площадь, первообразная, предел суммы, шаг разбиения, криволинейная трапеция</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">11-12</t>
@@ -465,12 +465,12 @@
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Вероятность в Excel; Статистика в Excel.</t>
+          <t xml:space="preserve">Две части в одной книге: расчёт вероятностей через функции Excel и статистическая сводка выборки. Сдаётся книга с формулами и выводами по каждому блоку.</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вероятность в Excel, Статистика в Excel</t>
+          <t xml:space="preserve">частота, выборка, среднее, медиана, стандартное отклонение</t>
         </is>
       </c>
     </row>
@@ -495,12 +495,12 @@
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Вероятность»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Случайное событие описывают числом от нуля до единицы. Правила сложения и умножения позволяют считать вероятность сложных событий через простые.</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Вероятность</t>
+          <t xml:space="preserve">событие, испытание, исход, независимость, условная вероятность</t>
         </is>
       </c>
     </row>
@@ -525,16 +525,16 @@
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Регрессия в Excel»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Построение линейной регрессии по опытным точкам в Excel: линия тренда, уравнение и коэффициент детерминации. Итог: лист с графиком и прогнозом.</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Регрессия в Excel</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="45" customHeight="1">
+          <t xml:space="preserve">линия тренда, коэффициент детерминации, прогноз, наблюдение, остаток</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1">
       <c r="A18" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">15</t>
@@ -555,16 +555,16 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Статистика»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Выборка описывается несколькими числами: среднее, медиана, мода, разброс. Они сжимают сотни наблюдений до сводки, по которой видно типичное и выбросы.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Статистика</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="45" customHeight="1">
+          <t xml:space="preserve">выборка, медиана, мода, дисперсия, выброс</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
@@ -585,12 +585,12 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Распределения»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Распределение показывает, с какой частотой встречаются значения величины. Нормальное, равномерное и биномиальное покрывают большинство учебных задач.</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Распределения</t>
+          <t xml:space="preserve">распределение, плотность, биномиальное, нормальное, квантиль</t>
         </is>
       </c>
     </row>
@@ -615,12 +615,12 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Линейное программирование; Python: массивы.</t>
+          <t xml:space="preserve">Задача линейного программирования решается в Python: массивы NumPy хранят коэффициенты, а оптимум ищется перебором вершин и проверкой ограничений.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Линейное программирование, Python: массивы</t>
+          <t xml:space="preserve">NumPy, индекс, ограничение, допустимое решение, целевая функция</t>
         </is>
       </c>
     </row>
@@ -645,12 +645,12 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Регрессия»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Метод наименьших квадратов подбирает прямую так, чтобы сумма квадратов отклонений была минимальной. По остаткам видно, где модель ошибается.</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Регрессия</t>
+          <t xml:space="preserve">наименьшие квадраты, парная регрессия, остаток, наклон, свободный член</t>
         </is>
       </c>
     </row>
@@ -675,16 +675,16 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Линейное программирование»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Задача с линейной целью и линейными ограничениями решается в вершинах допустимой области. Симплекс-метод перебирает вершины целенаправленно.</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Линейное программирование</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
+          <t xml:space="preserve">допустимая область, вершина, симплекс-метод, каноническая форма, базис</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">21-22</t>
@@ -705,12 +705,12 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Python: графики; Python: статистика.</t>
+          <t xml:space="preserve">Две части в одном ноутбуке: графики matplotlib по массивам данных и статистическая обработка той же выборки. Сдаётся ноутбук с графиками и сводкой.</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Python: графики, Python: статистика</t>
+          <t xml:space="preserve">matplotlib, диаграмма рассеяния, легенда, ось, сводка</t>
         </is>
       </c>
     </row>
@@ -735,12 +735,12 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Дискретные модели»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Дискретная модель меняет состояние шагами: очередь, склад, автомат. Граф состояний показывает, куда можно перейти и где процесс застревает.</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Дискретные модели</t>
+          <t xml:space="preserve">состояние, переход, граф, шаг, автомат</t>
         </is>
       </c>
     </row>
@@ -765,16 +765,16 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Python: регрессия»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Регрессия на Python: загрузка наблюдений, подгонка прямой, вывод коэффициентов и графика с остатками. Сдаётся скрипт и краткий отчёт с прогнозом.</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Python: регрессия</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="45" customHeight="1">
+          <t xml:space="preserve">pandas, коэффициент, остаток, прогноз, скрипт</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">25</t>
@@ -795,12 +795,12 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Имитационное моделирование»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Имитация прогоняет модель много раз со случайными входами и собирает распределение результатов. Так оценивают риск и разброс там, где формула слишком сложна.</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имитационное моделирование</t>
+          <t xml:space="preserve">имитация, прогон, случайное число, гистограмма, риск</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Colab: модель»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Сборка модели в Google Colab: ячейки кода, загрузка данных, расчёт и график. Сдаётся ссылка на ноутбук с выполненными ячейками и выводом.</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Colab: модель</t>
+          <t xml:space="preserve">ноутбук, ячейка, вывод, ссылка, график</t>
         </is>
       </c>
     </row>
@@ -855,12 +855,12 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Численные методы»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Когда точная формула недоступна, решение ищут приближениями: деление отрезка пополам, итерации, метод Ньютона. Важно оценить точность и число шагов.</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Численные методы</t>
+          <t xml:space="preserve">приближение, итерация, погрешность, сходимость, корень</t>
         </is>
       </c>
     </row>
@@ -885,16 +885,16 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Обработка эксперимента»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Опыт даёт таблицу измерений с шумом. Обработка включает отсев промахов, усреднение, оценку погрешности и проверку, согласуются ли данные с моделью.</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Обработка эксперимента</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="30" customHeight="1">
+          <t xml:space="preserve">измерение, погрешность, промах, среднее, доверительный интервал</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">29-30</t>
@@ -915,12 +915,12 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Имитационная модель; Численный метод.</t>
+          <t xml:space="preserve">Две связанные части: имитация случайного процесса и численное решение уравнения из этой модели. Сдаётся ноутбук с прогонами, графиком и оценкой точности.</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имитационная модель, Численный метод</t>
+          <t xml:space="preserve">прогон, итерация, сходимость, гистограмма, погрешность</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Excel для моделей»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Excel как среда модели: именованные ячейки, таблицы данных, сценарии и сводные расчёты. Одна книга хранит модель, варианты и результат сравнения.</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Excel для моделей</t>
+          <t xml:space="preserve">именованная ячейка, таблица данных, сценарий, сводная таблица, книга</t>
         </is>
       </c>
     </row>
@@ -975,16 +975,16 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Python и Colab»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Python даёт модели вычисления и графику: NumPy для массивов, pandas для таблиц, matplotlib для рисунков. Colab запускает тот же код без установки.</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Python и Colab</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="30" customHeight="1">
+          <t xml:space="preserve">NumPy, pandas, matplotlib, библиотека, скрипт</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="45" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">33-34</t>
@@ -1005,12 +1005,12 @@
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Совмещённая практическая работа: Визуализация; Проверка адекватности.</t>
+          <t xml:space="preserve">Две части: графическое представление результатов модели и проверка, совпадает ли модель с данными. Сдаётся отчёт с графиками и таблицей расхождений.</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Визуализация, Проверка адекватности</t>
+          <t xml:space="preserve">график, расхождение, адекватность, отчёт, масштаб</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Визуализация результатов»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">График выбирают по вопросу: сравнение, динамика, связь или распределение. Ошибки масштаба и лишние элементы прячут главный вывод.</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Визуализация результатов</t>
+          <t xml:space="preserve">диаграмма, масштаб, легенда, подпись, искажение</t>
         </is>
       </c>
     </row>
@@ -1065,16 +1065,16 @@
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Мини-проект»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Мини-проект по своей задаче: постановка, модель, расчёт и проверка на данных. Сдаётся отчёт с графиками и защитой выбранных допущений.</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Мини-проект</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="45" customHeight="1">
+          <t xml:space="preserve">задача, постановка, метод, результат, защита</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1">
       <c r="A36" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">37</t>
@@ -1095,16 +1095,16 @@
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Разбор темы «Оценка адекватности модели»: ключевые понятия, примеры и практические ситуации.</t>
+          <t xml:space="preserve">Модель адекватна, если её ошибка укладывается в допуск задачи. Проверяют по контрольным точкам, остаткам и поведению за пределами изученного диапазона.</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Оценка адекватности модели</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="45" customHeight="1">
+          <t xml:space="preserve">адекватность, контрольная точка, ошибка, допуск, границы применимости</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="60" customHeight="1">
       <c r="A37" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">38</t>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практическая работа «Итоговая модель»: выполнение задания, оформление и проверка результата.</t>
+          <t xml:space="preserve">Итоговая работа: собрать полную модель по выбранной задаче, провести расчёт и оформить отчёт. Сдаётся книга или ноутбук вместе с выводами и графиками.</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Итоговая модель</t>
+          <t xml:space="preserve">сборка, расчёт, отчёт, контроль, вывод</t>
         </is>
       </c>
     </row>

--- a/courses/2/math-modeling/dist/Учебный_план_Математическое_моделирование.xlsx
+++ b/courses/2/math-modeling/dist/Учебный_план_Математическое_моделирование.xlsx
@@ -160,7 +160,7 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Минуты</t>
+          <t xml:space="preserve">Часы</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -191,7 +191,7 @@
         </is>
       </c>
       <c r="D6" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
@@ -221,7 +221,7 @@
         </is>
       </c>
       <c r="D7" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
@@ -251,7 +251,7 @@
         </is>
       </c>
       <c r="D8" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
@@ -281,7 +281,7 @@
         </is>
       </c>
       <c r="D9" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
@@ -311,7 +311,7 @@
         </is>
       </c>
       <c r="D10" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
@@ -341,7 +341,7 @@
         </is>
       </c>
       <c r="D11" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
@@ -371,7 +371,7 @@
         </is>
       </c>
       <c r="D12" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="D13" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
@@ -431,7 +431,7 @@
         </is>
       </c>
       <c r="D14" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
@@ -461,7 +461,7 @@
         </is>
       </c>
       <c r="D15" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="D16" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="D17" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="D18" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
@@ -581,7 +581,7 @@
         </is>
       </c>
       <c r="D19" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="D20" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="D21" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
@@ -671,7 +671,7 @@
         </is>
       </c>
       <c r="D22" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="D23" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
         </is>
       </c>
       <c r="D24" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="D25" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="D26" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
         </is>
       </c>
       <c r="D27" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
         </is>
       </c>
       <c r="D28" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         </is>
       </c>
       <c r="D29" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="D30" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
@@ -941,7 +941,7 @@
         </is>
       </c>
       <c r="D31" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="D32" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="D33" s="6">
-        <v>180</v>
+        <v>4</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         </is>
       </c>
       <c r="D34" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="D35" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="D36" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="D37" s="6">
-        <v>90</v>
+        <v>2</v>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         </is>
       </c>
       <c r="D38" s="6">
-        <v>3420</v>
+        <v>76</v>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>

--- a/courses/2/math-modeling/dist/Учебный_план_Математическое_моделирование.xlsx
+++ b/courses/2/math-modeling/dist/Учебный_план_Математическое_моделирование.xlsx
@@ -212,12 +212,12 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 1. Постановка задачи</t>
+          <t xml:space="preserve">Лекция 2. Постановка задачи</t>
         </is>
       </c>
       <c r="D7" s="6">
@@ -225,12 +225,12 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Формулировка задачи для расчёта: что дано, что найти, какие ограничения учесть. Результат: постановка с переменными и критерием на листе Excel.</t>
+          <t xml:space="preserve">Переход от текста задачи к формальной постановке: какие величины известны, какие ищут, что ограничивает решение и как выглядит целевая функция.</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">переменная, исходные данные, ограничение, критерий, формулировка</t>
+          <t xml:space="preserve">целевая функция, параметр, ограничение, область допустимых значений, формализация</t>
         </is>
       </c>
     </row>
@@ -242,12 +242,12 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 2. Постановка задачи</t>
+          <t xml:space="preserve">Практика 1. Постановка задачи</t>
         </is>
       </c>
       <c r="D8" s="6">
@@ -255,12 +255,12 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Переход от текста задачи к формальной постановке: какие величины известны, какие ищут, что ограничивает решение и как выглядит целевая функция.</t>
+          <t xml:space="preserve">Формулировка задачи для расчёта: что дано, что найти, какие ограничения учесть. Результат: постановка с переменными и критерием на листе Excel.</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">целевая функция, параметр, ограничение, область допустимых значений, формализация</t>
+          <t xml:space="preserve">переменная, исходные данные, ограничение, критерий, формулировка</t>
         </is>
       </c>
     </row>
@@ -297,64 +297,64 @@
     <row r="10" ht="45" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">5-6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 2. Расчёты в Excel; Графики в Excel</t>
+          <t xml:space="preserve">Лекция 4. Функции и графики</t>
         </is>
       </c>
       <c r="D10" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Расчётная таблица в Excel: формулы, абсолютные ссылки, подбор параметра. Итог: книга с расчётом и двумя графиками по полученным значениям.</t>
+          <t xml:space="preserve">Функция связывает вход и выход модели, а её график показывает поведение связи: рост, насыщение, разрыв. Коэффициенты сдвигают и растягивают кривую.</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">формула, абсолютная ссылка, подбор параметра, диаграмма, оси координат</t>
+          <t xml:space="preserve">функция, аргумент, область определения, коэффициент, асимптота</t>
         </is>
       </c>
     </row>
     <row r="11" ht="45" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6-7</t>
         </is>
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 4. Функции и графики</t>
+          <t xml:space="preserve">Практика 2. Расчёты в Excel; Графики в Excel</t>
         </is>
       </c>
       <c r="D11" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Функция связывает вход и выход модели, а её график показывает поведение связи: рост, насыщение, разрыв. Коэффициенты сдвигают и растягивают кривую.</t>
+          <t xml:space="preserve">Расчётная таблица в Excel: формулы, абсолютные ссылки, подбор параметра. Итог: книга с расчётом и двумя графиками по полученным значениям.</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">функция, аргумент, область определения, коэффициент, асимптота</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="45" customHeight="1">
+          <t xml:space="preserve">формула, абсолютная ссылка, подбор параметра, диаграмма, оси координат</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="60" customHeight="1">
       <c r="A12" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">8</t>
@@ -362,55 +362,55 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Лекция 5. Производная и оптимизация</t>
+        </is>
+      </c>
+      <c r="D12" s="6">
+        <v>2</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Производная показывает скорость изменения величины, поэтому в точке максимума или минимума она обращается в нуль. Это даёт способ искать оптимум без перебора.</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">приращение, скорость изменения, экстремум, касательная, критическая точка</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="45" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Практика</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Практика 3. Оптимизация в Excel</t>
         </is>
       </c>
-      <c r="D12" s="6">
-        <v>2</v>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="D13" s="6">
+        <v>2</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Поиск наилучшего варианта в Excel через надстройку «Поиск решения»: задать целевую ячейку, переменные и ограничения, получить ответ и отчёт.</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">целевая ячейка, переменные, ограничение, Поиск решения, отчёт</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="60" customHeight="1">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция 5. Производная и оптимизация</t>
-        </is>
-      </c>
-      <c r="D13" s="6">
-        <v>2</v>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Производная показывает скорость изменения величины, поэтому в точке максимума или минимума она обращается в нуль. Это даёт способ искать оптимум без перебора.</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">приращение, скорость изменения, экстремум, касательная, критическая точка</t>
         </is>
       </c>
     </row>
@@ -444,93 +444,93 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="60" customHeight="1">
+    <row r="15" ht="45" customHeight="1">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">11-12</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Лекция 7. Вероятность</t>
+        </is>
+      </c>
+      <c r="D15" s="6">
+        <v>2</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Случайное событие описывают числом от нуля до единицы. Правила сложения и умножения позволяют считать вероятность сложных событий через простые.</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">событие, испытание, исход, независимость, условная вероятность</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="60" customHeight="1">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Лекция 8. Статистика</t>
+        </is>
+      </c>
+      <c r="D16" s="6">
+        <v>2</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Выборка описывается несколькими числами: среднее, медиана, мода, разброс. Они сжимают сотни наблюдений до сводки, по которой видно типичное и выбросы.</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">выборка, медиана, мода, дисперсия, выброс</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13-14</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Практика</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Практика 4. Вероятность в Excel; Статистика в Excel</t>
         </is>
       </c>
-      <c r="D15" s="6">
+      <c r="D17" s="6">
         <v>4</v>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Две части в одной книге: расчёт вероятностей через функции Excel и статистическая сводка выборки. Сдаётся книга с формулами и выводами по каждому блоку.</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">частота, выборка, среднее, медиана, стандартное отклонение</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="45" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">13</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция</t>
-        </is>
-      </c>
-      <c r="C16" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция 7. Вероятность</t>
-        </is>
-      </c>
-      <c r="D16" s="6">
-        <v>2</v>
-      </c>
-      <c r="E16" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Случайное событие описывают числом от нуля до единицы. Правила сложения и умножения позволяют считать вероятность сложных событий через простые.</t>
-        </is>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">событие, испытание, исход, независимость, условная вероятность</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="45" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Практика</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Практика 5. Регрессия в Excel</t>
-        </is>
-      </c>
-      <c r="D17" s="6">
-        <v>2</v>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Построение линейной регрессии по опытным точкам в Excel: линия тренда, уравнение и коэффициент детерминации. Итог: лист с графиком и прогнозом.</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">линия тренда, коэффициент детерминации, прогноз, наблюдение, остаток</t>
         </is>
       </c>
     </row>
@@ -547,7 +547,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 8. Статистика</t>
+          <t xml:space="preserve">Лекция 9. Распределения</t>
         </is>
       </c>
       <c r="D18" s="6">
@@ -555,16 +555,16 @@
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Выборка описывается несколькими числами: среднее, медиана, мода, разброс. Они сжимают сотни наблюдений до сводки, по которой видно типичное и выбросы.</t>
+          <t xml:space="preserve">Распределение показывает, с какой частотой встречаются значения величины. Нормальное, равномерное и биномиальное покрывают большинство учебных задач.</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">выборка, медиана, мода, дисперсия, выброс</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="60" customHeight="1">
+          <t xml:space="preserve">распределение, плотность, биномиальное, нормальное, квантиль</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="45" customHeight="1">
       <c r="A19" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">16</t>
@@ -577,7 +577,7 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 9. Распределения</t>
+          <t xml:space="preserve">Лекция 10. Регрессия</t>
         </is>
       </c>
       <c r="D19" s="6">
@@ -585,19 +585,19 @@
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Распределение показывает, с какой частотой встречаются значения величины. Нормальное, равномерное и биномиальное покрывают большинство учебных задач.</t>
+          <t xml:space="preserve">Метод наименьших квадратов подбирает прямую так, чтобы сумма квадратов отклонений была минимальной. По остаткам видно, где модель ошибается.</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">распределение, плотность, биномиальное, нормальное, квантиль</t>
+          <t xml:space="preserve">наименьшие квадраты, парная регрессия, остаток, наклон, свободный член</t>
         </is>
       </c>
     </row>
     <row r="20" ht="45" customHeight="1">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">17-18</t>
+          <t xml:space="preserve">17</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -607,27 +607,27 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 6. Линейное программирование; Python: массивы</t>
+          <t xml:space="preserve">Практика 5. Регрессия в Excel</t>
         </is>
       </c>
       <c r="D20" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Задача линейного программирования решается в Python: массивы NumPy хранят коэффициенты, а оптимум ищется перебором вершин и проверкой ограничений.</t>
+          <t xml:space="preserve">Построение линейной регрессии по опытным точкам в Excel: линия тренда, уравнение и коэффициент детерминации. Итог: лист с графиком и прогнозом.</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">NumPy, индекс, ограничение, допустимое решение, целевая функция</t>
+          <t xml:space="preserve">линия тренда, коэффициент детерминации, прогноз, наблюдение, остаток</t>
         </is>
       </c>
     </row>
     <row r="21" ht="45" customHeight="1">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 10. Регрессия</t>
+          <t xml:space="preserve">Лекция 11. Линейное программирование</t>
         </is>
       </c>
       <c r="D21" s="6">
@@ -645,79 +645,79 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Метод наименьших квадратов подбирает прямую так, чтобы сумма квадратов отклонений была минимальной. По остаткам видно, где модель ошибается.</t>
+          <t xml:space="preserve">Задача с линейной целью и линейными ограничениями решается в вершинах допустимой области. Симплекс-метод перебирает вершины целенаправленно.</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">наименьшие квадраты, парная регрессия, остаток, наклон, свободный член</t>
+          <t xml:space="preserve">допустимая область, вершина, симплекс-метод, каноническая форма, базис</t>
         </is>
       </c>
     </row>
     <row r="22" ht="45" customHeight="1">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">20</t>
+          <t xml:space="preserve">19-20</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 11. Линейное программирование</t>
+          <t xml:space="preserve">Практика 6. Линейное программирование; Python: массивы</t>
         </is>
       </c>
       <c r="D22" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Задача с линейной целью и линейными ограничениями решается в вершинах допустимой области. Симплекс-метод перебирает вершины целенаправленно.</t>
+          <t xml:space="preserve">Задача линейного программирования решается в Python: массивы NumPy хранят коэффициенты, а оптимум ищется перебором вершин и проверкой ограничений.</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">допустимая область, вершина, симплекс-метод, каноническая форма, базис</t>
+          <t xml:space="preserve">NumPy, индекс, ограничение, допустимое решение, целевая функция</t>
         </is>
       </c>
     </row>
     <row r="23" ht="45" customHeight="1">
       <c r="A23" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">21-22</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 7. Python: графики; статистика</t>
+          <t xml:space="preserve">Лекция 12. Дискретные модели</t>
         </is>
       </c>
       <c r="D23" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Две части в одном ноутбуке: графики matplotlib по массивам данных и статистическая обработка той же выборки. Сдаётся ноутбук с графиками и сводкой.</t>
+          <t xml:space="preserve">Дискретная модель меняет состояние шагами: очередь, склад, автомат. Граф состояний показывает, куда можно перейти и где процесс застревает.</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">matplotlib, диаграмма рассеяния, легенда, ось, сводка</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="45" customHeight="1">
+          <t xml:space="preserve">состояние, переход, граф, шаг, автомат</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">23</t>
+          <t xml:space="preserve">22</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 12. Дискретные модели</t>
+          <t xml:space="preserve">Лекция 13. Имитационное моделирование</t>
         </is>
       </c>
       <c r="D24" s="6">
@@ -735,29 +735,29 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Дискретная модель меняет состояние шагами: очередь, склад, автомат. Граф состояний показывает, куда можно перейти и где процесс застревает.</t>
+          <t xml:space="preserve">Имитация прогоняет модель много раз со случайными входами и собирает распределение результатов. Так оценивают риск и разброс там, где формула слишком сложна.</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">состояние, переход, граф, шаг, автомат</t>
+          <t xml:space="preserve">имитация, прогон, случайное число, гистограмма, риск</t>
         </is>
       </c>
     </row>
     <row r="25" ht="45" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">24</t>
+          <t xml:space="preserve">23</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 8. Python: регрессия</t>
+          <t xml:space="preserve">Лекция 14. Численные методы</t>
         </is>
       </c>
       <c r="D25" s="6">
@@ -765,42 +765,42 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Регрессия на Python: загрузка наблюдений, подгонка прямой, вывод коэффициентов и графика с остатками. Сдаётся скрипт и краткий отчёт с прогнозом.</t>
+          <t xml:space="preserve">Когда точная формула недоступна, решение ищут приближениями: деление отрезка пополам, итерации, метод Ньютона. Важно оценить точность и число шагов.</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">pandas, коэффициент, остаток, прогноз, скрипт</t>
+          <t xml:space="preserve">приближение, итерация, погрешность, сходимость, корень</t>
         </is>
       </c>
     </row>
     <row r="26" ht="60" customHeight="1">
       <c r="A26" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">25</t>
+          <t xml:space="preserve">24-25</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 13. Имитационное моделирование</t>
+          <t xml:space="preserve">Практика 7. Имитационная модель; Численный метод</t>
         </is>
       </c>
       <c r="D26" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Имитация прогоняет модель много раз со случайными входами и собирает распределение результатов. Так оценивают риск и разброс там, где формула слишком сложна.</t>
+          <t xml:space="preserve">Две связанные части: имитация случайного процесса и численное решение уравнения из этой модели. Сдаётся ноутбук с прогонами, графиком и оценкой точности.</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">имитация, прогон, случайное число, гистограмма, риск</t>
+          <t xml:space="preserve">прогон, итерация, сходимость, гистограмма, погрешность</t>
         </is>
       </c>
     </row>
@@ -812,12 +812,12 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 9. Colab: модель</t>
+          <t xml:space="preserve">Лекция 15. Обработка эксперимента</t>
         </is>
       </c>
       <c r="D27" s="6">
@@ -825,12 +825,12 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сборка модели в Google Colab: ячейки кода, загрузка данных, расчёт и график. Сдаётся ссылка на ноутбук с выполненными ячейками и выводом.</t>
+          <t xml:space="preserve">Опыт даёт таблицу измерений с шумом. Обработка включает отсев промахов, усреднение, оценку погрешности и проверку, согласуются ли данные с моделью.</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">ноутбук, ячейка, вывод, ссылка, график</t>
+          <t xml:space="preserve">измерение, погрешность, промах, среднее, доверительный интервал</t>
         </is>
       </c>
     </row>
@@ -847,7 +847,7 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 14. Численные методы</t>
+          <t xml:space="preserve">Лекция 16. Excel для моделей</t>
         </is>
       </c>
       <c r="D28" s="6">
@@ -855,12 +855,12 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Когда точная формула недоступна, решение ищут приближениями: деление отрезка пополам, итерации, метод Ньютона. Важно оценить точность и число шагов.</t>
+          <t xml:space="preserve">Excel как среда модели: именованные ячейки, таблицы данных, сценарии и сводные расчёты. Одна книга хранит модель, варианты и результат сравнения.</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">приближение, итерация, погрешность, сходимость, корень</t>
+          <t xml:space="preserve">именованная ячейка, таблица данных, сценарий, сводная таблица, книга</t>
         </is>
       </c>
     </row>
@@ -877,7 +877,7 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 15. Обработка эксперимента</t>
+          <t xml:space="preserve">Лекция 17. Python и Colab</t>
         </is>
       </c>
       <c r="D29" s="6">
@@ -885,16 +885,16 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Опыт даёт таблицу измерений с шумом. Обработка включает отсев промахов, усреднение, оценку погрешности и проверку, согласуются ли данные с моделью.</t>
+          <t xml:space="preserve">Python даёт модели вычисления и графику: NumPy для массивов, pandas для таблиц, matplotlib для рисунков. Colab запускает тот же код без установки.</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">измерение, погрешность, промах, среднее, доверительный интервал</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="60" customHeight="1">
+          <t xml:space="preserve">NumPy, pandas, matplotlib, библиотека, скрипт</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="45" customHeight="1">
       <c r="A30" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">29-30</t>
@@ -907,7 +907,7 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 10. Имитационная модель; Численный метод</t>
+          <t xml:space="preserve">Практика 8. Python: графики; статистика</t>
         </is>
       </c>
       <c r="D30" s="6">
@@ -915,12 +915,12 @@
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Две связанные части: имитация случайного процесса и численное решение уравнения из этой модели. Сдаётся ноутбук с прогонами, графиком и оценкой точности.</t>
+          <t xml:space="preserve">Две части в одном ноутбуке: графики matplotlib по массивам данных и статистическая обработка той же выборки. Сдаётся ноутбук с графиками и сводкой.</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">прогон, итерация, сходимость, гистограмма, погрешность</t>
+          <t xml:space="preserve">matplotlib, диаграмма рассеяния, легенда, ось, сводка</t>
         </is>
       </c>
     </row>
@@ -932,12 +932,12 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 16. Excel для моделей</t>
+          <t xml:space="preserve">Практика 9. Python: регрессия</t>
         </is>
       </c>
       <c r="D31" s="6">
@@ -945,12 +945,12 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Excel как среда модели: именованные ячейки, таблицы данных, сценарии и сводные расчёты. Одна книга хранит модель, варианты и результат сравнения.</t>
+          <t xml:space="preserve">Регрессия на Python: загрузка наблюдений, подгонка прямой, вывод коэффициентов и графика с остатками. Сдаётся скрипт и краткий отчёт с прогнозом.</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">именованная ячейка, таблица данных, сценарий, сводная таблица, книга</t>
+          <t xml:space="preserve">pandas, коэффициент, остаток, прогноз, скрипт</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция</t>
+          <t xml:space="preserve">Практика</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 17. Python и Colab</t>
+          <t xml:space="preserve">Практика 10. Colab: модель</t>
         </is>
       </c>
       <c r="D32" s="6">
@@ -975,49 +975,49 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Python даёт модели вычисления и графику: NumPy для массивов, pandas для таблиц, matplotlib для рисунков. Colab запускает тот же код без установки.</t>
+          <t xml:space="preserve">Сборка модели в Google Colab: ячейки кода, загрузка данных, расчёт и график. Сдаётся ссылка на ноутбук с выполненными ячейками и выводом.</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">NumPy, pandas, matplotlib, библиотека, скрипт</t>
+          <t xml:space="preserve">ноутбук, ячейка, вывод, ссылка, график</t>
         </is>
       </c>
     </row>
     <row r="33" ht="45" customHeight="1">
       <c r="A33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">33-34</t>
+          <t xml:space="preserve">33</t>
         </is>
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика</t>
+          <t xml:space="preserve">Лекция</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Практика 11. Визуализация; Проверка адекватности</t>
+          <t xml:space="preserve">Лекция 18. Визуализация результатов</t>
         </is>
       </c>
       <c r="D33" s="6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Две части: графическое представление результатов модели и проверка, совпадает ли модель с данными. Сдаётся отчёт с графиками и таблицей расхождений.</t>
+          <t xml:space="preserve">График выбирают по вопросу: сравнение, динамика, связь или распределение. Ошибки масштаба и лишние элементы прячут главный вывод.</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">график, расхождение, адекватность, отчёт, масштаб</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="45" customHeight="1">
+          <t xml:space="preserve">диаграмма, масштаб, легенда, подпись, искажение</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="60" customHeight="1">
       <c r="A34" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">35</t>
+          <t xml:space="preserve">34</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Лекция 18. Визуализация результатов</t>
+          <t xml:space="preserve">Лекция 19. Оценка адекватности модели</t>
         </is>
       </c>
       <c r="D34" s="6">
@@ -1035,19 +1035,19 @@
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">График выбирают по вопросу: сравнение, динамика, связь или распределение. Ошибки масштаба и лишние элементы прячут главный вывод.</t>
+          <t xml:space="preserve">Модель адекватна, если её ошибка укладывается в допуск задачи. Проверяют по контрольным точкам, остаткам и поведению за пределами изученного диапазона.</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">диаграмма, масштаб, легенда, подпись, искажение</t>
+          <t xml:space="preserve">адекватность, контрольная точка, ошибка, допуск, границы применимости</t>
         </is>
       </c>
     </row>
     <row r="35" ht="45" customHeight="1">
       <c r="A35" s="6" t="inlineStr">
         <is>
-          <t xml:space="preserve">36</t>
+          <t xml:space="preserve">35-36</t>
         </is>
       </c>
       <c r="B35" s="6" t="inlineStr">
@@ -1057,50 +1057,50 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
+          <t xml:space="preserve">Практика 11. Визуализация; Проверка адекватности</t>
+        </is>
+      </c>
+      <c r="D35" s="6">
+        <v>4</v>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Две части: графическое представление результатов модели и проверка, совпадает ли модель с данными. Сдаётся отчёт с графиками и таблицей расхождений.</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">график, расхождение, адекватность, отчёт, масштаб</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="45" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Практика</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Практика 12. Мини-проект</t>
         </is>
       </c>
-      <c r="D35" s="6">
-        <v>2</v>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="D36" s="6">
+        <v>2</v>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">Мини-проект по своей задаче: постановка, модель, расчёт и проверка на данных. Сдаётся отчёт с графиками и защитой выбранных допущений.</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">задача, постановка, метод, результат, защита</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="60" customHeight="1">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">37</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Лекция 19. Оценка адекватности модели</t>
-        </is>
-      </c>
-      <c r="D36" s="6">
-        <v>2</v>
-      </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Модель адекватна, если её ошибка укладывается в допуск задачи. Проверяют по контрольным точкам, остаткам и поведению за пределами изученного диапазона.</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">адекватность, контрольная точка, ошибка, допуск, границы применимости</t>
         </is>
       </c>
     </row>
